--- a/output/full_scan/batch_seq7_2026-07-28.xlsx
+++ b/output/full_scan/batch_seq7_2026-07-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -951,21 +951,21 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6811</v>
+        <v>6727</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>529.3643006496359</v>
+        <v>532.3910896393494</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>224</v>
+        <v>343</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>47.5980980816986</v>
+        <v>38.59320283273484</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24.93165554936182</v>
+        <v>14.65054332588844</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5718121727401311</v>
+        <v>0.1212281871346348</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,51 +994,51 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.293388506045531</v>
+        <v>-5.881753746365728</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6806</v>
+        <v>6811</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>529.3643006496359</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.51</v>
+        <v>224</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>31.69502890222169</v>
+        <v>47.5980980816986</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32.5931979585683</v>
+        <v>24.93165554936182</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.5718121727401311</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,48 +1047,48 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.411282151645155</v>
+        <v>0.293388506045531</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6753</v>
+        <v>6806</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>526.3007418853055</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>133</v>
+        <v>3.51</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44.46905495067108</v>
+        <v>31.69502890222169</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>29.0044753109734</v>
+        <v>32.5931979585683</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.3822191540811209</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-2.351021147055249</v>
+        <v>0.411282151645155</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6548</v>
+        <v>6753</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>506.0448922104577</v>
+        <v>526.3007418853055</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>32.15249416810975</v>
+        <v>44.46905495067108</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.82803034107348</v>
+        <v>29.0044753109734</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3782864939128259</v>
+        <v>0.3822191540811209</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-2.188946171529957</v>
+        <v>-2.351021147055249</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6525</v>
+        <v>6548</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>494.463314590264</v>
+        <v>506.0448922104577</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>36.84066722439776</v>
+        <v>32.15249416810975</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.68939563151051</v>
+        <v>25.82803034107348</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4504104443938004</v>
+        <v>0.3782864939128259</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-7.957940283070462</v>
+        <v>-2.188946171529957</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6491</v>
+        <v>6525</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>466.2386806744961</v>
+        <v>494.463314590264</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>323.5</v>
+        <v>128</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>39.97398961943318</v>
+        <v>36.84066722439776</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.8302546036531</v>
+        <v>27.68939563151051</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6376521458668477</v>
+        <v>0.4504104443938004</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-4.879389440861924</v>
+        <v>-7.957940283070462</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6643</v>
+        <v>6491</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>464.8390490483042</v>
+        <v>466.2386806744961</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>416</v>
+        <v>323.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>39.63197908160009</v>
+        <v>39.97398961943318</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19.67080996224336</v>
+        <v>22.8302546036531</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.975220811322976</v>
+        <v>0.6376521458668477</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.157802111012355</v>
+        <v>-4.879389440861924</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6534</v>
+        <v>6643</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>463.2704341972449</v>
+        <v>464.8390490483042</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>92.7</v>
+        <v>416</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>52.18780126402236</v>
+        <v>39.63197908160009</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21.55189952929215</v>
+        <v>19.67080996224336</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.469850487346755</v>
+        <v>1.975220811322976</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0465215633815593</v>
+        <v>2.157802111012355</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6504</v>
+        <v>6534</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>462.2285173853609</v>
+        <v>463.2704341972449</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>39.7</v>
+        <v>92.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.11431214144072</v>
+        <v>52.18780126402236</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.11901055424078</v>
+        <v>21.55189952929215</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8961063723296356</v>
+        <v>1.469850487346755</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.4989616746053095</v>
+        <v>0.0465215633815593</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6834</v>
+        <v>6504</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>460.2543821332953</v>
+        <v>462.2285173853609</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>82.3</v>
+        <v>39.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>36.36742456075599</v>
+        <v>67.11431214144072</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.900490463131</v>
+        <v>23.11901055424078</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4862756000096871</v>
+        <v>0.8961063723296356</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-5.077779089947832</v>
+        <v>0.4989616746053095</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6651</v>
+        <v>6834</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>457.5716555787587</v>
+        <v>460.2543821332953</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>114.5</v>
+        <v>82.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>35.44904337228768</v>
+        <v>36.36742456075599</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.32105063517156</v>
+        <v>25.900490463131</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4379707987846266</v>
+        <v>0.4862756000096871</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.936181265439632</v>
+        <v>-5.077779089947832</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6488</v>
+        <v>6651</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>454.6535441540212</v>
+        <v>457.5716555787587</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>959</v>
+        <v>114.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.35179372270148</v>
+        <v>35.44904337228768</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>19.78252450572827</v>
+        <v>25.32105063517156</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6087194297625016</v>
+        <v>0.4379707987846266</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-55.44459363168905</v>
+        <v>-2.936181265439632</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6669</v>
+        <v>6488</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>451.3834596824272</v>
+        <v>454.6535441540212</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5315</v>
+        <v>959</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.84137631896949</v>
+        <v>40.35179372270148</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.05975626639547</v>
+        <v>19.78252450572827</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.032255013296271</v>
+        <v>0.6087194297625016</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>70.49352900052196</v>
+        <v>-55.44459363168905</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6512</v>
+        <v>6669</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>450.7741192174434</v>
+        <v>451.3834596824272</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>19.7</v>
+        <v>5315</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.05609775576156</v>
+        <v>53.84137631896949</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9.792359552002971</v>
+        <v>15.05975626639547</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7737798045024354</v>
+        <v>1.032255013296271</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1477959140336997</v>
+        <v>70.49352900052196</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6720</v>
+        <v>6512</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>450.0203567412418</v>
+        <v>450.7741192174434</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>138</v>
+        <v>19.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>44.73515452615589</v>
+        <v>52.05609775576156</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.42272796940706</v>
+        <v>9.792359552002971</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.519050535237489</v>
+        <v>0.7737798045024354</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1214045663377705</v>
+        <v>0.1477959140336997</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6829</v>
+        <v>6720</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>448.4220032965214</v>
+        <v>450.0203567412418</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>38.17625940331838</v>
+        <v>44.73515452615589</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.40378480917077</v>
+        <v>26.42272796940706</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3253786943957117</v>
+        <v>2.519050535237489</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-5.289937501888614</v>
+        <v>0.1214045663377705</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6517</v>
+        <v>6829</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>432.8268934883114</v>
+        <v>448.4220032965214</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>60.6</v>
+        <v>180</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>38.01467262417718</v>
+        <v>38.17625940331838</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.86012853118431</v>
+        <v>15.40378480917077</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5433333188133367</v>
+        <v>0.3253786943957117</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.153199150064683</v>
+        <v>-5.289937501888614</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6581</v>
+        <v>6517</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>427.1177260299432</v>
+        <v>432.8268934883114</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>108.5</v>
+        <v>60.6</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.06317183381594</v>
+        <v>38.01467262417718</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9.55811392083773</v>
+        <v>20.86012853118431</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.220487771842647</v>
+        <v>0.5433333188133367</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1271194147674055</v>
+        <v>-1.153199150064683</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6498</v>
+        <v>6581</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>421.7485178183396</v>
+        <v>427.1177260299432</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>74</v>
+        <v>108.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>24.82928671178026</v>
+        <v>56.06317183381594</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>34.45877288328543</v>
+        <v>9.55811392083773</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.018508911954904</v>
+        <v>1.220487771842647</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.7748689071169625</v>
+        <v>0.1271194147674055</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6606</v>
+        <v>6498</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>418.1081019294422</v>
+        <v>421.7485178183396</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>25.9</v>
+        <v>74</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.73207749398706</v>
+        <v>24.82928671178026</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.20686888684804</v>
+        <v>34.45877288328543</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3956812324034023</v>
+        <v>2.018508911954904</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0562352772138306</v>
+        <v>-0.7748689071169625</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6584</v>
+        <v>6606</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>416.1315267543497</v>
+        <v>418.1081019294422</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>482</v>
+        <v>25.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>28.57385634960561</v>
+        <v>57.73207749398706</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.04997852297315</v>
+        <v>14.20686888684804</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4865649506690404</v>
+        <v>0.3956812324034023</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-16.34213074365381</v>
+        <v>0.0562352772138306</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6654</v>
+        <v>6584</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>415.6483762759082</v>
+        <v>416.1315267543497</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>166</v>
+        <v>482</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>39.5469435963363</v>
+        <v>28.57385634960561</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.05675586289757</v>
+        <v>25.04997852297315</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.405906865160557</v>
+        <v>0.4865649506690404</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-3.606473145867132</v>
+        <v>-16.34213074365381</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6743</v>
+        <v>6654</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>413.6803508249013</v>
+        <v>415.6483762759082</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>29.8</v>
+        <v>166</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46.67597024252622</v>
+        <v>39.5469435963363</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.40859533110562</v>
+        <v>25.05675586289757</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8471942968577109</v>
+        <v>1.405906865160557</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0817866371201523</v>
+        <v>-3.606473145867132</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6693</v>
+        <v>6743</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>412.3559097130616</v>
+        <v>413.6803508249013</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>155.5</v>
+        <v>29.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>33.50092350849054</v>
+        <v>46.67597024252622</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.59266083528191</v>
+        <v>30.40859533110562</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8956479845179248</v>
+        <v>0.8471942968577109</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-8.924239597542309</v>
+        <v>-0.0817866371201523</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6756</v>
+        <v>6693</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>401.9824105071909</v>
+        <v>412.3559097130616</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>89.7</v>
+        <v>155.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>40.12314968819256</v>
+        <v>33.50092350849054</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.33137698895965</v>
+        <v>30.59266083528191</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6585552487844534</v>
+        <v>0.8956479845179248</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.6236055264066351</v>
+        <v>-8.924239597542309</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6761</v>
+        <v>6756</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>397.9859367663141</v>
+        <v>401.9824105071909</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>138.5</v>
+        <v>89.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>28.34754057778627</v>
+        <v>40.12314968819256</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>25.94886441768348</v>
+        <v>20.33137698895965</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7389761403169172</v>
+        <v>0.6585552487844534</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-2.358301487276012</v>
+        <v>-0.6236055264066351</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6788</v>
+        <v>6761</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>394.5906412851335</v>
+        <v>397.9859367663141</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>311</v>
+        <v>138.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>26.81635052239551</v>
+        <v>28.34754057778627</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.74353378900891</v>
+        <v>25.94886441768348</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9200046531399528</v>
+        <v>0.7389761403169172</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>2</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-6.293347186738433</v>
+        <v>-2.358301487276012</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2382,21 +2382,21 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6716</v>
+        <v>6788</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>392.4332611577406</v>
+        <v>394.5906412851335</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>76.8</v>
+        <v>311</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>34.39343484936713</v>
+        <v>26.81635052239551</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.15092479040469</v>
+        <v>29.74353378900891</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4842052112325651</v>
+        <v>0.9200046531399528</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.400287279789696</v>
+        <v>-6.293347186738433</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6664</v>
+        <v>6716</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>385.4676890338681</v>
+        <v>392.4332611577406</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>330.5</v>
+        <v>76.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>36.76191593626439</v>
+        <v>34.39343484936713</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23.23078875491006</v>
+        <v>21.15092479040469</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.098557125700111</v>
+        <v>0.4842052112325651</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-2.732691532985772</v>
+        <v>-1.400287279789696</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6510</v>
+        <v>6683</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>382.8118243431498</v>
+        <v>388.6574210023638</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2480</v>
+        <v>1040</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>35.10450047514179</v>
+        <v>29.41105814066123</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.38925068142956</v>
+        <v>25.94292886721518</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5956593578033699</v>
+        <v>0.243249514075476</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-5.250898499966013</v>
+        <v>-39.14035839188709</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6570</v>
+        <v>6664</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>380.9340059911011</v>
+        <v>385.4676890338681</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>47.75</v>
+        <v>330.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>41.39847554448374</v>
+        <v>36.76191593626439</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.28630016204199</v>
+        <v>23.23078875491006</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5258120479413191</v>
+        <v>1.098557125700111</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0592603616076403</v>
+        <v>-2.732691532985772</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6533</v>
+        <v>6510</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>380.7889604865667</v>
+        <v>382.8118243431498</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>204.5</v>
+        <v>2480</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45.31801341988103</v>
+        <v>35.10450047514179</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.78143453975771</v>
+        <v>31.38925068142956</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6799473297237727</v>
+        <v>0.5956593578033699</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.2638280532511317</v>
+        <v>-5.250898499966013</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6672</v>
+        <v>6570</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>378.8935686374126</v>
+        <v>380.9340059911011</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>199.5</v>
+        <v>47.75</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>32.45512195440264</v>
+        <v>41.39847554448374</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.01380549170685</v>
+        <v>16.28630016204199</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5284745476732282</v>
+        <v>0.5258120479413191</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-9.465661508989257</v>
+        <v>-0.0592603616076403</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6782</v>
+        <v>6533</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>372.9155418406403</v>
+        <v>380.7889604865667</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>178</v>
+        <v>204.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>31.36594072215657</v>
+        <v>45.31801341988103</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.64705558857225</v>
+        <v>16.78143453975771</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.084951892246778</v>
+        <v>0.6799473297237727</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.456256100482994</v>
+        <v>-0.2638280532511317</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6741</v>
+        <v>6672</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>371.394086061209</v>
+        <v>378.8935686374126</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>54.5</v>
+        <v>199.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>32.19827321205855</v>
+        <v>32.45512195440264</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27.33364586463719</v>
+        <v>28.01380549170685</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5680083574540573</v>
+        <v>0.5284745476732282</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.2824606135960261</v>
+        <v>-9.465661508989257</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6613</v>
+        <v>6782</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>370.7240790495142</v>
+        <v>372.9155418406403</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>282.5</v>
+        <v>178</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>36.42652935153734</v>
+        <v>31.36594072215657</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.93917600174952</v>
+        <v>21.64705558857225</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.807587114158475</v>
+        <v>1.084951892246778</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-8.640414399598406</v>
+        <v>-2.456256100482994</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6560</v>
+        <v>6741</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>370.5499619384434</v>
+        <v>371.394086061209</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>31.65</v>
+        <v>54.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>28.37913281090394</v>
+        <v>32.19827321205855</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>27.59979426816625</v>
+        <v>27.33364586463719</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.712723703617817</v>
+        <v>0.5680083574540573</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>3</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.3817718432978081</v>
+        <v>-0.2824606135960261</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2912,21 +2912,21 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6790</v>
+        <v>6613</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>368.0278970126024</v>
+        <v>370.7240790495142</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>39.1</v>
+        <v>282.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.41557495064111</v>
+        <v>36.42652935153734</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.2601783090651</v>
+        <v>17.93917600174952</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7606582633562129</v>
+        <v>0.807587114158475</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0434686626275154</v>
+        <v>-8.640414399598406</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6830</v>
+        <v>6560</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>365.1858985310941</v>
+        <v>370.5499619384434</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>374</v>
+        <v>31.65</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>36.2645460048146</v>
+        <v>28.37913281090394</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>29.08326853821336</v>
+        <v>27.59979426816625</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.052928442506188</v>
+        <v>0.712723703617817</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>6.424850596619208</v>
+        <v>-0.3817718432978081</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6763</v>
+        <v>6790</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>365.075715189301</v>
+        <v>368.0278970126024</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>41.6</v>
+        <v>39.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>33.96419825446777</v>
+        <v>46.41557495064111</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>30.38405990539684</v>
+        <v>22.2601783090651</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6498938488422146</v>
+        <v>0.7606582633562129</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.1652052589677621</v>
+        <v>-0.0434686626275154</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6670</v>
+        <v>6830</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>357.6655420725317</v>
+        <v>365.1858985310941</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>268</v>
+        <v>374</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.15540582638832</v>
+        <v>36.2645460048146</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13.37577200196381</v>
+        <v>29.08326853821336</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5044316347353804</v>
+        <v>2.052928442506188</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.561975407654725</v>
+        <v>6.424850596619208</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6799</v>
+        <v>6763</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>356.9451007226679</v>
+        <v>365.075715189301</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>77.5</v>
+        <v>41.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>32.5806544642539</v>
+        <v>33.96419825446777</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.63424372231979</v>
+        <v>30.38405990539684</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6816128601438327</v>
+        <v>0.6498938488422146</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.578860527042015</v>
+        <v>-0.1652052589677621</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6757</v>
+        <v>6670</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>356.7307286161353</v>
+        <v>357.6655420725317</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>54.7</v>
+        <v>268</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>40.7803574449221</v>
+        <v>54.15540582638832</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.38532735490027</v>
+        <v>13.37577200196381</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.552444772695918</v>
+        <v>0.5044316347353804</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.5979964930167256</v>
+        <v>1.561975407654725</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6515</v>
+        <v>6799</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>354.7389965084543</v>
+        <v>356.9451007226679</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>5935</v>
+        <v>77.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>33.61872360694967</v>
+        <v>32.5806544642539</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.64686116110092</v>
+        <v>25.63424372231979</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5926341581758183</v>
+        <v>0.6816128601438327</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-80.39387914078657</v>
+        <v>-1.578860527042015</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6658</v>
+        <v>6757</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>354.4296223105075</v>
+        <v>356.7307286161353</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>144.5</v>
+        <v>54.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>32.43266223656238</v>
+        <v>40.7803574449221</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.45572397777291</v>
+        <v>20.38532735490027</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3355287726295629</v>
+        <v>1.552444772695918</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-3.762083529732061</v>
+        <v>-0.5979964930167256</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6807</v>
+        <v>6515</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>352.4748726006607</v>
+        <v>354.7389965084543</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>34.1</v>
+        <v>5935</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>55.94241786363661</v>
+        <v>33.61872360694967</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.13773498675563</v>
+        <v>23.64686116110092</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.183889445665266</v>
+        <v>0.5926341581758183</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0911325834909692</v>
+        <v>-80.39387914078657</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6640</v>
+        <v>6658</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>350.6710370222428</v>
+        <v>354.4296223105075</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>871</v>
+        <v>144.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>37.18677261998797</v>
+        <v>32.43266223656238</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.06389589022318</v>
+        <v>23.45572397777291</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5228782109777518</v>
+        <v>0.3355287726295629</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.3355994496549854</v>
+        <v>-3.762083529732061</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6735</v>
+        <v>6807</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>347.7278932451567</v>
+        <v>352.4748726006607</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>62.2</v>
+        <v>34.1</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>21.80892926953139</v>
+        <v>55.94241786363661</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>30.11478168715896</v>
+        <v>14.13773498675563</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8278405257742459</v>
+        <v>0.183889445665266</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.5055000865210957</v>
+        <v>0.0911325834909692</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6558</v>
+        <v>6640</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>345.3372934530123</v>
+        <v>350.6710370222428</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>24.9</v>
+        <v>871</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>29.14469603480264</v>
+        <v>37.18677261998797</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>26.83649344731354</v>
+        <v>20.06389589022318</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.548294286839433</v>
+        <v>0.5228782109777518</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.2794644249027522</v>
+        <v>-0.3355994496549854</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6680</v>
+        <v>6735</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>332.6796666907269</v>
+        <v>347.7278932451567</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>55</v>
+        <v>62.2</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.23567779414751</v>
+        <v>21.80892926953139</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.101018478567696</v>
+        <v>30.11478168715896</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3821535359813243</v>
+        <v>0.8278405257742459</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1136600213297338</v>
+        <v>-0.5055000865210957</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6715</v>
+        <v>6558</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>329.7373401854661</v>
+        <v>345.3372934530123</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>360</v>
+        <v>24.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.20796808155258</v>
+        <v>29.14469603480264</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>10.87566084468409</v>
+        <v>26.83649344731354</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.03222457721662</v>
+        <v>1.548294286839433</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.442807579533305</v>
+        <v>-0.2794644249027522</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6579</v>
+        <v>6680</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>328.5278987955249</v>
+        <v>332.6796666907269</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>162.5</v>
+        <v>55</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.23972274189187</v>
+        <v>52.23567779414751</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.68842490300316</v>
+        <v>9.101018478567696</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.667575776180113</v>
+        <v>0.3821535359813243</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.5694458875436954</v>
+        <v>-0.1136600213297338</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6585</v>
+        <v>6715</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>328.0630815001652</v>
+        <v>329.7373401854661</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>113</v>
+        <v>360</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>37.38125192078982</v>
+        <v>40.20796808155258</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.69231191489913</v>
+        <v>10.87566084468409</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.151577613826731</v>
+        <v>1.03222457721662</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.731673987279876</v>
+        <v>-1.442807579533305</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6494</v>
+        <v>6579</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>323.1456723931814</v>
+        <v>328.5278987955249</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46.3</v>
+        <v>162.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>26.39170147975973</v>
+        <v>49.23972274189187</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>31.99437829116036</v>
+        <v>16.68842490300316</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6949640258742025</v>
+        <v>0.667575776180113</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.581093543310495</v>
+        <v>0.5694458875436954</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6719</v>
+        <v>6585</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>322.5869761721006</v>
+        <v>328.0630815001652</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>208.5</v>
+        <v>113</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>37.52902163489475</v>
+        <v>37.38125192078982</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.36158110722712</v>
+        <v>22.69231191489913</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4231820215617007</v>
+        <v>1.151577613826731</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-5.790160640055479</v>
+        <v>-1.731673987279876</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6803</v>
+        <v>6494</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>321.636011958178</v>
+        <v>323.1456723931814</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>271</v>
+        <v>46.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>37.9523722744118</v>
+        <v>26.39170147975973</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>44.24713019445131</v>
+        <v>31.99437829116036</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5215809407900875</v>
+        <v>0.6949640258742025</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2799842426680747</v>
+        <v>-1.581093543310495</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6532</v>
+        <v>6719</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>321.1656143579536</v>
+        <v>322.5869761721006</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>64.7</v>
+        <v>208.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>25.17818915985553</v>
+        <v>37.52902163489475</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>34.34349205337148</v>
+        <v>21.36158110722712</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5298016727150677</v>
+        <v>0.4231820215617007</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.5653864188869866</v>
+        <v>-5.790160640055479</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6739</v>
+        <v>6803</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>318.6304758502741</v>
+        <v>321.636011958178</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>941</v>
+        <v>271</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>37.00275823374015</v>
+        <v>37.9523722744118</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>10.22452025862199</v>
+        <v>44.24713019445131</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.115113878184704</v>
+        <v>0.5215809407900875</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-12.6197387176614</v>
+        <v>0.2799842426680747</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6732</v>
+        <v>6532</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>318.1660681599326</v>
+        <v>321.1656143579536</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>155.5</v>
+        <v>64.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>36.5752366330536</v>
+        <v>25.17818915985553</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>26.29291022653021</v>
+        <v>34.34349205337148</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4019343688538973</v>
+        <v>0.5298016727150677</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-5.468526002607756</v>
+        <v>-0.5653864188869866</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6568</v>
+        <v>6739</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>316.030567060629</v>
+        <v>318.6304758502741</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>133.5</v>
+        <v>941</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>28.78747491720162</v>
+        <v>37.00275823374015</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>49.76595092517886</v>
+        <v>10.22452025862199</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.011132881071837</v>
+        <v>1.115113878184704</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>2</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2477684506637256</v>
+        <v>-12.6197387176614</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6805</v>
+        <v>6732</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>310.1125933928253</v>
+        <v>318.1660681599326</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1340</v>
+        <v>155.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>39.04078146822541</v>
+        <v>36.5752366330536</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>35.10139533941339</v>
+        <v>26.29291022653021</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.08144430195207</v>
+        <v>0.4019343688538973</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>10.16051777666101</v>
+        <v>-5.468526002607756</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6821</v>
+        <v>6568</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>304.0209237632954</v>
+        <v>316.030567060629</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>40.05</v>
+        <v>133.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>22.57129867706981</v>
+        <v>28.78747491720162</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>29.72674716811558</v>
+        <v>49.76595092517886</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3923901706479797</v>
+        <v>1.011132881071837</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6753427557487894</v>
+        <v>0.2477684506637256</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6781</v>
+        <v>6805</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>302.1979313209969</v>
+        <v>310.1125933928253</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>915</v>
+        <v>1340</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>33.35464146393767</v>
+        <v>39.04078146822541</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.10866585101506</v>
+        <v>35.10139533941339</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4725667730035209</v>
+        <v>1.08144430195207</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-12.14993116999805</v>
+        <v>10.16051777666101</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6530</v>
+        <v>6821</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>302.1539818609133</v>
+        <v>304.0209237632954</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>40.05</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>31.18506857046043</v>
+        <v>22.57129867706981</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>30.90919739391557</v>
+        <v>29.72674716811558</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.122596754542359</v>
+        <v>0.3923901706479797</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.2458091058764555</v>
+        <v>-0.6753427557487894</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6742</v>
+        <v>6781</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>298.7162496982425</v>
+        <v>302.1979313209969</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>40.55</v>
+        <v>915</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>25.2033444206173</v>
+        <v>33.35464146393767</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>24.61209162435116</v>
+        <v>22.10866585101506</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4887029216430773</v>
+        <v>0.4725667730035209</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.461846564555047</v>
+        <v>-12.14993116999805</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6789</v>
+        <v>6530</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>296.4730568916277</v>
+        <v>302.1539818609133</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>424</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>35.560259115245</v>
+        <v>31.18506857046043</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.17743312462125</v>
+        <v>30.90919739391557</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8065962014540977</v>
+        <v>1.122596754542359</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-6.987672701951167</v>
+        <v>0.2458091058764555</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6526</v>
+        <v>6742</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>294.9926703033468</v>
+        <v>298.7162496982425</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>532</v>
+        <v>40.55</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>32.97321581029777</v>
+        <v>25.2033444206173</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.99557447120772</v>
+        <v>24.61209162435116</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8070304922203904</v>
+        <v>0.4887029216430773</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-8.623032405172061</v>
+        <v>-1.461846564555047</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6706</v>
+        <v>6789</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>293.6623927206016</v>
+        <v>296.4730568916277</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>102</v>
+        <v>424</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>28.18824704271512</v>
+        <v>35.560259115245</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>30.68486729487777</v>
+        <v>15.17743312462125</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.878051885338735</v>
+        <v>0.8065962014540977</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.173042739696514</v>
+        <v>-6.987672701951167</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6725</v>
+        <v>6526</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>293.3243397764532</v>
+        <v>294.9926703033468</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>265</v>
+        <v>532</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>34.68394750377297</v>
+        <v>32.97321581029777</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.75960428091722</v>
+        <v>18.99557447120772</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8446156127519325</v>
+        <v>0.8070304922203904</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-4.358671508123164</v>
+        <v>-8.623032405172061</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6531</v>
+        <v>6706</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>292.9177391348007</v>
+        <v>293.6623927206016</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>696</v>
+        <v>102</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.27348510804775</v>
+        <v>28.18824704271512</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.76503475678452</v>
+        <v>30.68486729487777</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2484083316361292</v>
+        <v>0.878051885338735</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-15.60076260124649</v>
+        <v>-1.173042739696514</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6754</v>
+        <v>6725</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>291.2831724434391</v>
+        <v>293.3243397764532</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>42.6</v>
+        <v>265</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.64376691874732</v>
+        <v>34.68394750377297</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.04891910244826</v>
+        <v>13.75960428091722</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3569660784936216</v>
+        <v>0.8446156127519325</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0716880828601023</v>
+        <v>-4.358671508123164</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6691</v>
+        <v>6531</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>289.4899017946946</v>
+        <v>292.9177391348007</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>645</v>
+        <v>696</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>37.0848743739724</v>
+        <v>34.27348510804775</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.26437673509801</v>
+        <v>16.76503475678452</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.095501731388569</v>
+        <v>0.2484083316361292</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-9.629722713299079</v>
+        <v>-15.60076260124649</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6792</v>
+        <v>6754</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>287.3949820761571</v>
+        <v>291.2831724434391</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>51</v>
+        <v>42.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>28.29758327691937</v>
+        <v>45.64376691874732</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.55072758959381</v>
+        <v>11.04891910244826</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8877481575671828</v>
+        <v>0.3569660784936216</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.593833468774684</v>
+        <v>0.0716880828601023</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6573</v>
+        <v>6691</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>287.1877014276192</v>
+        <v>289.4899017946946</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>16.75</v>
+        <v>645</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.51584092523154</v>
+        <v>37.0848743739724</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.98707573792824</v>
+        <v>16.26437673509801</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3051975792925318</v>
+        <v>1.095501731388569</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.013593852585396</v>
+        <v>-9.629722713299079</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6770</v>
+        <v>6792</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>286.0902153520059</v>
+        <v>287.3949820761571</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>55.8</v>
+        <v>51</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>33.82675680562386</v>
+        <v>28.29758327691937</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15.72455716279093</v>
+        <v>24.55072758959381</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6477510955579635</v>
+        <v>0.8877481575671828</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.563714436263491</v>
+        <v>-0.593833468774684</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6667</v>
+        <v>6573</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>284.7470238246705</v>
+        <v>287.1877014276192</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>233</v>
+        <v>16.75</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>33.60556248320667</v>
+        <v>38.51584092523154</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>21.52222111005109</v>
+        <v>19.98707573792824</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7940677961245222</v>
+        <v>0.3051975792925318</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.564912174194072</v>
+        <v>-1.013593852585396</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6695</v>
+        <v>6770</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>277.1809393710495</v>
+        <v>286.0902153520059</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>49.1</v>
+        <v>55.8</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.69807515605554</v>
+        <v>33.82675680562386</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.85734366583348</v>
+        <v>15.72455716279093</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7838914790865114</v>
+        <v>0.6477510955579635</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.7334888626193736</v>
+        <v>-1.563714436263491</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6550</v>
+        <v>6667</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>276.7917473532208</v>
+        <v>284.7470238246705</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>11.45</v>
+        <v>233</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>31.66278062379641</v>
+        <v>33.60556248320667</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.78576241722138</v>
+        <v>21.52222111005109</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.00427096512052</v>
+        <v>0.7940677961245222</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0472060315456802</v>
+        <v>-1.564912174194072</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6835</v>
+        <v>6695</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>273.784720817632</v>
+        <v>277.1809393710495</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>30.2</v>
+        <v>49.1</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>24.55720666256241</v>
+        <v>39.69807515605554</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>43.00752791993397</v>
+        <v>15.85734366583348</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9180969488615978</v>
+        <v>0.7838914790865114</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1449891766335029</v>
+        <v>-0.7334888626193736</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6657</v>
+        <v>6550</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>259.4999028383734</v>
+        <v>276.7917473532208</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>31.8</v>
+        <v>11.45</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>35.55887005046456</v>
+        <v>31.66278062379641</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.10655927927975</v>
+        <v>20.78576241722138</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.60441542543492</v>
+        <v>1.00427096512052</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.2104937850915629</v>
+        <v>-0.0472060315456802</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6552</v>
+        <v>6835</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.8837968685983</v>
+        <v>273.784720817632</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>23.95</v>
+        <v>30.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>30.32876812654069</v>
+        <v>24.55720666256241</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.04020690784637</v>
+        <v>43.00752791993397</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.268561955671502</v>
+        <v>0.9180969488615978</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.3055020164672877</v>
+        <v>-0.1449891766335029</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6624</v>
+        <v>6657</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>253.4861808682597</v>
+        <v>259.4999028383734</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>37.89302899141099</v>
+        <v>35.55887005046456</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9.984829852201798</v>
+        <v>20.10655927927975</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0</v>
+        <v>1.60441542543492</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-4.022097077169622</v>
+        <v>-0.2104937850915629</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6698</v>
+        <v>6552</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>253.254920092183</v>
+        <v>255.8837968685983</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>31.95</v>
+        <v>23.95</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>29.36488960953311</v>
+        <v>30.32876812654069</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.75032723922854</v>
+        <v>20.04020690784637</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5295618224439065</v>
+        <v>1.268561955671502</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.7831854987084677</v>
+        <v>-0.3055020164672877</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6561</v>
+        <v>6624</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>252.5067168714093</v>
+        <v>253.4861808682597</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>321.5</v>
+        <v>0</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.3891514617206</v>
+        <v>37.89302899141099</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.78026885268832</v>
+        <v>9.984829852201798</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.147331446907098</v>
+        <v>0</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.3468626802926122</v>
+        <v>-4.022097077169622</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6645</v>
+        <v>6698</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>251.8485350943901</v>
+        <v>253.254920092183</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>13.5</v>
+        <v>31.95</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.34487341624504</v>
+        <v>29.36488960953311</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26.08727419042033</v>
+        <v>21.75032723922854</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.939273898610566</v>
+        <v>0.5295618224439065</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2224263516367274</v>
+        <v>-0.7831854987084677</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6690</v>
+        <v>6561</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>248.8479831761851</v>
+        <v>252.5067168714093</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>159.5</v>
+        <v>321.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.87468653587357</v>
+        <v>39.3891514617206</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>22.08874153813916</v>
+        <v>24.78026885268832</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.033052754446343</v>
+        <v>1.147331446907098</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0147007998637018</v>
+        <v>0.3468626802926122</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6689</v>
+        <v>6645</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>246.606002691526</v>
+        <v>251.8485350943901</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>59.1</v>
+        <v>13.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>33.89137432195538</v>
+        <v>39.34487341624504</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.89773113391408</v>
+        <v>26.08727419042033</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.294964872246906</v>
+        <v>0.939273898610566</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1304065910083629</v>
+        <v>-0.2224263516367274</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6768</v>
+        <v>6690</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>244.434671671999</v>
+        <v>248.8479831761851</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>159.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.23846111766429</v>
+        <v>37.87468653587357</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>35.51719356454901</v>
+        <v>22.08874153813916</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5706648440378737</v>
+        <v>1.033052754446343</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.5452626509771354</v>
+        <v>-0.0147007998637018</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6642</v>
+        <v>6689</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>244.2611037289474</v>
+        <v>246.606002691526</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>71.5</v>
+        <v>59.1</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>37.36138074401051</v>
+        <v>33.89137432195538</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.38168935498648</v>
+        <v>23.89773113391408</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9411611547059332</v>
+        <v>1.294964872246906</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.6961707606144976</v>
+        <v>-0.1304065910083629</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6776</v>
+        <v>6768</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>242.6317040482834</v>
+        <v>244.434671671999</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>52.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>34.14902806019255</v>
+        <v>37.23846111766429</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.24625675594532</v>
+        <v>35.51719356454901</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.666352826205775</v>
+        <v>0.5706648440378737</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0157061692180748</v>
+        <v>0.5452626509771354</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6840</v>
+        <v>6642</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>229.5560901642536</v>
+        <v>244.2611037289474</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>59</v>
+        <v>71.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.27464762653474</v>
+        <v>37.36138074401051</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.30832951868444</v>
+        <v>18.38168935498648</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.422240288489057</v>
+        <v>0.9411611547059332</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1893429432471303</v>
+        <v>-0.6961707606144976</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6546</v>
+        <v>6776</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>228.5563014145609</v>
+        <v>242.6317040482834</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>57.5</v>
+        <v>52.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>30.02208990013612</v>
+        <v>34.14902806019255</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>31.13733664116693</v>
+        <v>19.24625675594532</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.975069326646642</v>
+        <v>1.666352826205775</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.4617900517691593</v>
+        <v>-0.0157061692180748</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6722</v>
+        <v>6840</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>222.0539118133667</v>
+        <v>229.5560901642536</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>33.6</v>
+        <v>59</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>38.15434777166677</v>
+        <v>39.27464762653474</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>38.27620708244802</v>
+        <v>12.30832951868444</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.068023134104744</v>
+        <v>1.422240288489057</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.09341364847293129</v>
+        <v>-0.1893429432471303</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6486</v>
+        <v>6546</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>218.8783911545582</v>
+        <v>228.5563014145609</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>76.5</v>
+        <v>57.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>37.39259630209482</v>
+        <v>30.02208990013612</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.2352809256123</v>
+        <v>31.13733664116693</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.042870620214978</v>
+        <v>0.975069326646642</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3276342897842097</v>
+        <v>-0.4617900517691593</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6823</v>
+        <v>6722</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>212.9381233701793</v>
+        <v>222.0539118133667</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>63.4</v>
+        <v>33.6</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.04233602040932</v>
+        <v>38.15434777166677</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>14.93209367190391</v>
+        <v>38.27620708244802</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7521495308837415</v>
+        <v>1.068023134104744</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0943257033231219</v>
+        <v>0.09341364847293129</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6655</v>
+        <v>6486</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>210.6360247655637</v>
+        <v>218.8783911545582</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>117.5</v>
+        <v>76.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.8793814461201</v>
+        <v>37.39259630209482</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>5.643710936145204</v>
+        <v>18.2352809256123</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4509252422314035</v>
+        <v>1.042870620214978</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.09346081115639771</v>
+        <v>-0.3276342897842097</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6556</v>
+        <v>6823</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>207.1874885930659</v>
+        <v>212.9381233701793</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>34.92345194191454</v>
+        <v>43.04233602040932</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>29.72262242978578</v>
+        <v>14.93209367190391</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.37631585590589</v>
+        <v>0.7521495308837415</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2427653253114652</v>
+        <v>0.0943257033231219</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6589</v>
+        <v>6655</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>207.0147772205339</v>
+        <v>210.6360247655637</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>45.95</v>
+        <v>117.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.47073071536152</v>
+        <v>48.8793814461201</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.88260644349206</v>
+        <v>5.643710936145204</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4106028897436066</v>
+        <v>0.4509252422314035</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.2545764468653097</v>
+        <v>0.09346081115639771</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6582</v>
+        <v>6556</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>200.0774670962717</v>
+        <v>207.1874885930659</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>31.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.81737683894029</v>
+        <v>34.92345194191454</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>22.5672940612019</v>
+        <v>29.72262242978578</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.117543464197816</v>
+        <v>1.37631585590589</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1428820759617144</v>
+        <v>-0.2427653253114652</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6605</v>
+        <v>6589</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>196.6597223797636</v>
+        <v>207.0147772205339</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>130</v>
+        <v>45.95</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.29151955533865</v>
+        <v>47.47073071536152</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.3888228892455</v>
+        <v>17.88260644349206</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5462426283046112</v>
+        <v>0.4106028897436066</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.21765888216756</v>
+        <v>-0.2545764468653097</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6591</v>
+        <v>6582</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>192.2143753035834</v>
+        <v>200.0774670962717</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>43.85</v>
+        <v>31.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>30.13546316776897</v>
+        <v>40.81737683894029</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>42.57287502015907</v>
+        <v>22.5672940612019</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8318492773889887</v>
+        <v>1.117543464197816</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0976903775958444</v>
+        <v>-0.1428820759617144</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6625</v>
+        <v>6605</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>188.3116956190128</v>
+        <v>196.6597223797636</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>32.72575127988807</v>
+        <v>43.29151955533865</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.0458934137015</v>
+        <v>12.3888228892455</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7699944299085626</v>
+        <v>0.5462426283046112</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.5613708919448497</v>
+        <v>0.21765888216756</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6641</v>
+        <v>6591</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>178.1490011525399</v>
+        <v>192.2143753035833</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>17.3</v>
+        <v>43.85</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>33.92152863473386</v>
+        <v>30.13546316776897</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.89823654714576</v>
+        <v>42.57287502015907</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5184019596096756</v>
+        <v>0.8318492773889887</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0683970155852828</v>
+        <v>-0.0976903775958444</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6671</v>
+        <v>6625</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>177.0225303591133</v>
+        <v>188.3116956190128</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>22.75</v>
+        <v>74</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>31.63296610616224</v>
+        <v>32.72575127988807</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>28.2591696811147</v>
+        <v>20.0458934137015</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8827881335529822</v>
+        <v>0.7699944299085626</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.08853116127289611</v>
+        <v>-0.5613708919448497</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6541</v>
+        <v>6641</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>174.283780132472</v>
+        <v>178.1490011525399</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>38.4</v>
+        <v>17.3</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.59865713759443</v>
+        <v>33.92152863473386</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>10.14231357131339</v>
+        <v>12.89823654714576</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.142105708262373</v>
+        <v>0.5184019596096756</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1628329310842609</v>
+        <v>-0.0683970155852828</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6668</v>
+        <v>6671</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>172.4791209664536</v>
+        <v>177.0225303591133</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>33.8</v>
+        <v>22.75</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>35.19697802000292</v>
+        <v>31.63296610616224</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.91044899511441</v>
+        <v>28.2591696811147</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>2.291242266125036</v>
+        <v>0.8827881335529822</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2227611067574988</v>
+        <v>-0.08853116127289611</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6592</v>
+        <v>6541</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>169.3092901797878</v>
+        <v>174.283780132472</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>60.3</v>
+        <v>38.4</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.57235261107195</v>
+        <v>42.59865713759443</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.59398607622323</v>
+        <v>10.14231357131339</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4279235489594667</v>
+        <v>1.142105708262373</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0797422973317041</v>
+        <v>-0.1628329310842609</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6597</v>
+        <v>6668</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>163.1521698287166</v>
+        <v>172.4791209664536</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0</v>
+        <v>33.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>27.03911313204414</v>
+        <v>35.19697802000292</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12.42684033832807</v>
+        <v>19.91044899511441</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.0028298149301035</v>
+        <v>2.291242266125036</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-3.590089263106304</v>
+        <v>-0.2227611067574988</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6796</v>
+        <v>6592</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>153.6653317604845</v>
+        <v>169.3092901797878</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>56.9</v>
+        <v>60.3</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>42.27966679511422</v>
+        <v>44.57235261107195</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.14867671848387</v>
+        <v>15.59398607622323</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.200041752047773</v>
+        <v>0.4279235489594667</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,28 +6718,28 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.087623728075962</v>
+        <v>0.0797422973317041</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6708</v>
+        <v>6597</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>148.7312651367978</v>
+        <v>163.1521698287166</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>0</v>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>33.06665816132269</v>
+        <v>27.03911313204414</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.92589534105378</v>
+        <v>12.42684033832807</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0</v>
+        <v>0.0028298149301035</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-2.633640008211971</v>
+        <v>-3.590089263106304</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6684</v>
+        <v>6796</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>140.9037514837594</v>
+        <v>153.6653317604845</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>47.7</v>
+        <v>56.9</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.14077104641586</v>
+        <v>42.27966679511422</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.40589449139938</v>
+        <v>14.14867671848387</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3648712828382627</v>
+        <v>1.200041752047773</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.8123277367521649</v>
+        <v>0.087623728075962</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6614</v>
+        <v>6708</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>109.914900376263</v>
+        <v>148.7312651367978</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>31.84165835722761</v>
+        <v>33.06665816132269</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>17.10388118390927</v>
+        <v>17.92589534105378</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.260492523426858</v>
+        <v>0</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1370909460009981</v>
+        <v>-2.633640008211971</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6692</v>
+        <v>6684</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>101.7609864817123</v>
+        <v>140.9037514837594</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0</v>
+        <v>47.7</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>8.845759169527682</v>
+        <v>39.14077104641586</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.59070620013442</v>
+        <v>18.40589449139938</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.0112468860184336</v>
+        <v>0.3648712828382627</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-1.525861797135531</v>
+        <v>-0.8123277367521649</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6674</v>
+        <v>6614</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>95.17243659640479</v>
+        <v>109.914900376263</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>15.65</v>
+        <v>37.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>34.84866500736177</v>
+        <v>31.84165835722761</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.86875858505515</v>
+        <v>17.10388118390927</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.2294537824760944</v>
+        <v>1.260492523426858</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0401446100683147</v>
+        <v>-0.1370909460009981</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6771</v>
+        <v>6692</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>84.43951237445307</v>
+        <v>101.7609864817123</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>36.45729942740024</v>
+        <v>8.845759169527682</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.07377247649997</v>
+        <v>19.59070620013442</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.7147005981167546</v>
+        <v>0.0112468860184336</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0434921843867399</v>
+        <v>-1.525861797135531</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,52 +7046,158 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6674</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>鋐寶科技</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>95.17243659640479</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>34.84866500736177</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>17.86875858505515</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.2294537824760944</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.0401446100683147</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6771</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>平和環保-創</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>84.43951237445307</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>36.45729942740024</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>12.07377247649997</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.7147005981167546</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.0434921843867399</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
         <v>6794</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>向榮生技-創</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>80.8866757972647</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>76.3</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
         <v>39.16639891069363</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>12.83171762093876</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J127" s="2" t="n">
         <v>0.6327616847901735</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
         <v>-0.2560171902526004</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
